--- a/7- Advance Excel/3-xloopup.xlsx
+++ b/7- Advance Excel/3-xloopup.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/7- Advance Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048C8291E62A85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B87CEAB0-F951-4938-944F-28C9F1159CBB}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC1048C8291E62A85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF4CBE46-F90C-49F5-9763-1A0E442F7855}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="WildCard match" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="WildCard match" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
   <si>
     <t>ProductID</t>
   </si>
@@ -147,6 +148,213 @@
   </si>
   <si>
     <t xml:space="preserve">Pen dom </t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Experience (Years)</t>
+  </si>
+  <si>
+    <t>E101</t>
+  </si>
+  <si>
+    <t>Rahul Sharma</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Jabalpur</t>
+  </si>
+  <si>
+    <t>E102</t>
+  </si>
+  <si>
+    <t>Priya Verma</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Bhopal</t>
+  </si>
+  <si>
+    <t>E103</t>
+  </si>
+  <si>
+    <t>Aman Khan</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Indore</t>
+  </si>
+  <si>
+    <t>E104</t>
+  </si>
+  <si>
+    <t>Neha Patel</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>E105</t>
+  </si>
+  <si>
+    <t>Rohit Singh</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>E106</t>
+  </si>
+  <si>
+    <t>Sneha Gupta</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>E107</t>
+  </si>
+  <si>
+    <t>Arjun Yadav</t>
+  </si>
+  <si>
+    <t>E108</t>
+  </si>
+  <si>
+    <t>Pooja Jain</t>
+  </si>
+  <si>
+    <t>E109</t>
+  </si>
+  <si>
+    <t>Karan Mehta</t>
+  </si>
+  <si>
+    <t>E110</t>
+  </si>
+  <si>
+    <t>Anjali Das</t>
+  </si>
+  <si>
+    <t>E111</t>
+  </si>
+  <si>
+    <t>Vikram Rao</t>
+  </si>
+  <si>
+    <t>E112</t>
+  </si>
+  <si>
+    <t>Simran Kaur</t>
+  </si>
+  <si>
+    <t>E113</t>
+  </si>
+  <si>
+    <t>Deepak Joshi</t>
+  </si>
+  <si>
+    <t>E114</t>
+  </si>
+  <si>
+    <t>Kavita Roy</t>
+  </si>
+  <si>
+    <t>E115</t>
+  </si>
+  <si>
+    <t>Mohit Sahu</t>
+  </si>
+  <si>
+    <t>Monthly Salary</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1. Find Rahul Sharma's Employee ID using his name.</t>
+  </si>
+  <si>
+    <t>2. Find the department of employee E108.</t>
+  </si>
+  <si>
+    <t>3. Find the monthly salary of employee E111.</t>
+  </si>
+  <si>
+    <t>4. Find the bonus of employee E104.</t>
+  </si>
+  <si>
+    <t>5. Find the city of employee E115.</t>
+  </si>
+  <si>
+    <t>6. Find the performance rating of employee E102.</t>
+  </si>
+  <si>
+    <t>7. Find the status of employee E110.</t>
+  </si>
+  <si>
+    <t>8. Find the employee name for ID E113.</t>
+  </si>
+  <si>
+    <t>9. Return both Monthly Salary and Bonus for E106.</t>
+  </si>
+  <si>
+    <t>10. Return Department, City, and Experience for E101.</t>
+  </si>
+  <si>
+    <t>11. Display Not Found when employee ID E120 does not exist.</t>
+  </si>
+  <si>
+    <t>12. Search for E109 and return salary; if missing, show 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Departments  Biils </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depatment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total  Salary  </t>
   </si>
 </sst>
 </file>
@@ -178,7 +386,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -186,17 +394,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -213,6 +501,1276 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$R$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total  Salary  </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:separator>, </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$O$3:$O$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sales</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$R$3:$R$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>87000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>121000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>154000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>92000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5D03-4A29-A076-A3B36D33132A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$P$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Salary </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="3"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="4"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$O$3:$O$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>IT</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>HR</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Sales</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Finance</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Marketing</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$P$3:$P$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>195000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>72000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>100000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>144000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>81000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-5D03-4A29-A076-A3B36D33132A}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Q$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Bonus </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="3"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="4"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$O$3:$O$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>IT</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>HR</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Sales</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Finance</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Marketing</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Q$3:$Q$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>30000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>21000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>11000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-5D03-4A29-A076-A3B36D33132A}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+          </c:ext>
+        </c:extLst>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73811BFB-651C-E4B9-7E2E-24E9C2181228}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,6 +2035,806 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F149B7E1-83CE-4694-B97D-971D0AAA4A10}">
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="20.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="9" width="14.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="14" max="14" width="3.77734375" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="16" width="9.21875" customWidth="1"/>
+    <col min="18" max="18" width="13.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="2">
+        <v>32000</v>
+      </c>
+      <c r="J2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="K2" s="2">
+        <v>4</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="2">
+        <v>45000</v>
+      </c>
+      <c r="J3" s="2">
+        <v>8000</v>
+      </c>
+      <c r="K3" s="2">
+        <v>5</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O3" t="str" cm="1">
+        <f t="array" ref="O3:O7">_xlfn.UNIQUE(C2:C16)</f>
+        <v>IT</v>
+      </c>
+      <c r="P3">
+        <f>SUMIF($C$2:$C$16,O3,$I$2:$I$16)</f>
+        <v>195000</v>
+      </c>
+      <c r="Q3">
+        <f ca="1">SUMIF($C$1:$C$16,O3,$J$2:$J$16)</f>
+        <v>30000</v>
+      </c>
+      <c r="R3">
+        <f ca="1">P3 + Q3</f>
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="2">
+        <v>28000</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3000</v>
+      </c>
+      <c r="K4" s="2">
+        <v>3</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O4" t="str">
+        <v>HR</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:P7" si="0">SUMIF($C$2:$C$16,O4,$I$2:$I$16)</f>
+        <v>72000</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q7" ca="1" si="1">SUMIF($C$1:$C$16,O4,$J$2:$J$16)</f>
+        <v>15000</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R7" ca="1" si="2">P4 + Q4</f>
+        <v>87000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="2">
+        <v>55000</v>
+      </c>
+      <c r="J5" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K5" s="2">
+        <v>5</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ca="1" si="1"/>
+        <v>21000</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ca="1" si="2"/>
+        <v>121000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="2">
+        <v>25000</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2000</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>144000</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" ca="1" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="R6">
+        <f t="shared" ca="1" si="2"/>
+        <v>154000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="2">
+        <v>48000</v>
+      </c>
+      <c r="J7" s="2">
+        <v>9000</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>81000</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" ca="1" si="1"/>
+        <v>11000</v>
+      </c>
+      <c r="R7">
+        <f t="shared" ca="1" si="2"/>
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4000</v>
+      </c>
+      <c r="K8" s="2">
+        <v>4</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="2">
+        <v>35000</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5000</v>
+      </c>
+      <c r="K9" s="2">
+        <v>4</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="2">
+        <v>50000</v>
+      </c>
+      <c r="J10" s="2">
+        <v>8500</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="2">
+        <v>27000</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2500</v>
+      </c>
+      <c r="K11" s="2">
+        <v>3</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="2">
+        <v>65000</v>
+      </c>
+      <c r="J12" s="2">
+        <v>12000</v>
+      </c>
+      <c r="K12" s="2">
+        <v>5</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="2">
+        <v>33000</v>
+      </c>
+      <c r="J13" s="2">
+        <v>4500</v>
+      </c>
+      <c r="K13" s="2">
+        <v>4</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="2">
+        <v>42000</v>
+      </c>
+      <c r="J14" s="2">
+        <v>7000</v>
+      </c>
+      <c r="K14" s="2">
+        <v>4</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="2">
+        <v>39000</v>
+      </c>
+      <c r="J15" s="2">
+        <v>6000</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="2">
+        <v>38000</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5500</v>
+      </c>
+      <c r="K16" s="2">
+        <v>4</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>_xlfn.XLOOKUP("Rahul Sharma",B2:B16,A2:A16, "Not Found ")</f>
+        <v>E101</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="G21" s="12" t="str">
+        <f>_xlfn.XLOOKUP("E110",H2:H16,L2:L16, "No Sattus" )</f>
+        <v>Inactive</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>_xlfn.XLOOKUP("E108",A2:A16,C2:C16,"Not Found" )</f>
+        <v>IT</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="G22" s="12" t="str">
+        <f>_xlfn.XLOOKUP("E113", A2:A16,  B2:B16, "Not Found")</f>
+        <v>Deepak Joshi</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f>_xlfn.XLOOKUP("E111", H2:H16, I2:I16)</f>
+        <v>65000</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="G23" s="4" cm="1">
+        <f t="array" ref="G23:H23">_xlfn.XLOOKUP("E106",H2:H16,I2:J16,"Not Found")</f>
+        <v>48000</v>
+      </c>
+      <c r="H23" s="4">
+        <v>9000</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f>_xlfn.XLOOKUP("E104", H2:H16,J2:J16, " no Bouns")</f>
+        <v>10000</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="G24" s="4" t="str" cm="1">
+        <f t="array" ref="G24:I24">_xlfn.XLOOKUP("E101", A2:A16,C2:E16)</f>
+        <v>IT</v>
+      </c>
+      <c r="H24" s="4" t="str">
+        <v>Jabalpur</v>
+      </c>
+      <c r="I24" s="5">
+        <v>2</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>_xlfn.XLOOKUP("E115", A2:A16,D2:D16,"Not Found")</f>
+        <v>Jabalpur</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="G25" s="12" t="str">
+        <f>_xlfn.XLOOKUP("E120",H2:H16,I2:I16,"Not Found" )</f>
+        <v>Not Found</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="10"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f>_xlfn.XLOOKUP("E102", H2:H16,K2:K16, "No  Rating")</f>
+        <v>5</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="G26" s="12">
+        <f>_xlfn.XLOOKUP("E109",H2:H16,I2:I16,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="I21:M21"/>
+    <mergeCell ref="I23:M23"/>
+    <mergeCell ref="I25:M25"/>
+    <mergeCell ref="I26:M26"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="J24:M24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2287D2D2-0A89-48ED-9A52-986BE5D1EF1B}">
   <dimension ref="A2:L16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -565,7 +2923,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J7" si="0">_xlfn.XLOOKUP(H4,$B$3:$B$7,$A$3:$A$7)</f>
+        <f t="shared" ref="J4:J6" si="0">_xlfn.XLOOKUP(H4,$B$3:$B$7,$A$3:$A$7)</f>
         <v>50</v>
       </c>
     </row>
@@ -774,7 +3132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F712AEF-9189-4D10-BF9F-7C7E71820B2E}">
   <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
